--- a/results/Supplementary_Tables.xlsx
+++ b/results/Supplementary_Tables.xlsx
@@ -28,6 +28,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7 CAD LOO (Python)" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7 CAD LOO (R)" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7 CAD substitutes" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S8 Extended estimators" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9 Heterogeneity I2 NOME" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S10 Influence diagnostics" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S11 Radial MR" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S12 Cross-dataset concordance" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21270,6 +21275,9399 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>nsnp</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pval</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>OR_lo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OR_hi</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Maximum likelihood</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0455242980468788</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.09875540083669471</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.644812711744347</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.04657643406826</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8623998199605321</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.27008634161956</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MR-Lasso</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0393604277803318</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0507206772059108</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.43773522307981</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.0401453133631</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.94171546936032</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.14886322685781</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>valid instruments: 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Contamination mixture</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0597852149968232</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0612244897959183</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.06160850447022</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9415622784073781</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.19696024640007</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CI 0.932-1.185; valid 33</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Debiased IVW</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>48</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0445504368161828</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.09226194607237929</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.629188729768546</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.04555770998262</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8725956726188721</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.2528035139381</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IVW (random effects, MendelianRandomization)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0442499540014544</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0973719921419226</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.64951049839029</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0452435850559</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.863640097658439</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2650340750304</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IVW (fixed effect)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>48</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0442499540014544</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0466471366832192</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.342818853968498</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.0452435850559</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.953917171244842</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.14531343499643</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MR-RAPS (tukey, overdispersed)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>48</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0323351492785422</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0561693494995539</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.564836573410632</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.03286361079737</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.925189427692932</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.15306898952529</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MR-RAPS (huber, overdispersed)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>48</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0215989722953545</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.074648423701517</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.772319181885649</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.02183391858125</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.882751152884631</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.18283001245716</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IVW, variants with F&gt;=30</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>47</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0450199703368693</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.09864169834372161</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.648103100353223</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.04604874964604</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.862157113731742</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.26916309012386</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IVW, variants with MAF&gt;=0.01</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>48</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0442499540014544</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0973719921419226</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.64951049839029</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.0452435850559</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.863640097658439</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.2650340750304</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Radial IVW (modified second order weights)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>48</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0442481452508754</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0973721724883978</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.649524471295853</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.04524169447267</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.863638230272214</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.26503223406372</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>radial outliers: rs157580;rs112875651;rs58542926;rs4665972;rs56325564;rs553427;rs2326077;rs2737245</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Maximum likelihood</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>51</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.0009078635078399</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.131166938563906</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9944775375521619</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.99909254847555</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.772599046347079</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.29198440658047</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MR-Lasso</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>51</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0158983350885026</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0658102491775724</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.809106856141707</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.01602538602427</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.893070500494634</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.15590827876861</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>valid instruments: 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Contamination mixture</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>51</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.0061368559315684</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.10969387755102</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.993881936107797</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.801606968114612</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.23227634266292</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CI 0.766-1.178; valid 41</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Debiased IVW</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>51</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.0009087370319843</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.122343478903416</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.994073565775394</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.999091675744468</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.786075876926191</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.2698318391923</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IVW (random effects, MendelianRandomization)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>51</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.0009024697161361</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.128691635711924</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9944047587293789</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.999097937387183</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.776360677869794</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.28573833907999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IVW (fixed effect)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>51</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.0009024697161361</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0573951675968734</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.987454745528586</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.999097937387183</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.892796151280597</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.11805666619367</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MR-RAPS (tukey, overdispersed)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>51</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0102169557209993</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0695552215133671</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.883218967333218</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.01026932701955</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.881516747512269</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.15782725171916</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MR-RAPS (huber, overdispersed)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>51</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.008597849105272001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.110773884140007</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.938133347196711</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.991439006696834</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.797945753414965</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.23185229045117</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IVW, variants with F&gt;=30</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.0067976812034626</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.129584784740578</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.958164236500994</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.993225370768515</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7704474266699241</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2804204453017</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IVW, variants with MAF&gt;=0.01</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>51</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.0009024697161361</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.128691635711924</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9944047587293789</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.999097937387183</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.776360677869794</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.28573833907999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Radial IVW (modified second order weights)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>51</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.0009024685679132</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.128691635486495</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.994404765838353</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.99909793853437</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.776360679104257</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.28573833998821</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>radial outliers: rs157580;rs112875651;rs58542926;rs1883711;rs4665972;rs1169292;rs2326077</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Maximum likelihood</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>48</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.166868562240718</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.212027828975283</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.431274519852637</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.846310841227751</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.558532144521585</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.28236493996801</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MR-Lasso</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>48</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.175857357810556</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.150894508859372</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.243843986702639</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.838737614174324</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.623996452843259</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.12737946221554</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>valid instruments: 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Contamination mixture</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>48</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0607563870448615</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.209183673469388</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.06264000977921</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.705221308294835</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.60120486590781</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>CI 0.698-1.585; valid 38</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Debiased IVW</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>48</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.16633476548758</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.200029755527688</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.405662931694903</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.846762719801873</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.572127685381682</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.25322916888374</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IVW (random effects, MendelianRandomization)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>48</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.165156736230421</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.210464335580192</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.432614513818046</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.847760818839178</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.561206227550987</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.28063155873226</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IVW (fixed effect)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>48</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.165156736230421</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.14003418157571</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.238237734357568</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.847760818839178</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6442787968989681</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.11550839390975</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MR-RAPS (tukey, overdispersed)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>48</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.141532285807792</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.152417966543122</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.353106755181016</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.868027150174754</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6438615887797799</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.17023774452589</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MR-RAPS (huber, overdispersed)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>48</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.155538420215381</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.188811983613995</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.410067931585231</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.855954190352828</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.591194679962542</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.23928310049912</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IVW, variants with F&gt;=30</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>47</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.149198189387372</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.210277000137901</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.477994610490792</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.861398377963581</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.570443523308392</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.30075482539425</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IVW, variants with MAF&gt;=0.01</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>48</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.165156736230421</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.210464335580192</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.432614513818046</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.847760818839178</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.561206227550987</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.28063155873226</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Radial IVW (modified second order weights)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>48</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.16515046315458</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.210466634391658</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.432637019701496</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.84776613692377</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.561207219430763</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.28064536240935</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>radial outliers: rs112875651;rs58542926;rs6601299</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nsnp</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Q_IVW</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Q_IVW_p</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>I2_IVW</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Q_Egger</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Q_Egger_p</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>I2_GX</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Egger_intercept</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Egger_intercept_se</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Egger_intercept_p</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>phi_random_effects</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C2" t="n">
+        <v>204.793414498689</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.37440570280507e-21</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.770500432765132</v>
+      </c>
+      <c r="F2" t="n">
+        <v>199.186699590528</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.81205868352579e-21</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.993469760731544</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0112325233689554</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0098712998912677</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.255163458731848</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.35730669146146</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>51</v>
+      </c>
+      <c r="C3" t="n">
+        <v>251.37378787303</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.24787580043992e-28</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.801093023966145</v>
+      </c>
+      <c r="F3" t="n">
+        <v>239.034225014661</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.0844361126769e-27</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.993330999885305</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0210800095698185</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0132541817092843</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.111735170373296</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.0274757574606</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>48</v>
+      </c>
+      <c r="C4" t="n">
+        <v>106.166321064529</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.81404631171622e-06</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.55729840189684</v>
+      </c>
+      <c r="F4" t="n">
+        <v>106.157947260988</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.17270460156151e-06</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.993469760731544</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.0012926460437525</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0214593013112994</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.951966799131148</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.25885789498997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F148"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SNP</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cooks_d</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>student_resid</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hat</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cook_threshold_4_over_n</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>rs72654473</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0342717412791544</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.333036969277759</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.232628456325598</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rs12151108</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.003173062225616</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.205118450882423</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0687971498142574</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rs157580</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0699870037385094</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.12744176519637</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0524710472320232</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rs11591147</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0069730638433757</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.339154209359339</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0561410965557233</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rs12740374</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0081814895900742</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.377053456362264</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0534759295971144</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rs693</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0159599308328505</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.551587786312819</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0491406602175695</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rs261290</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0040298629229927</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.298876845301573</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0423650975739935</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rs112875651</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.301797889023175</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.03699873594531</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0370226931808726</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rs58542926</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.520922567360154</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-5.13676308865383</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0295083307212453</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rs247616</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0026803062486716</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.311238468415841</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0264206091038646</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rs12916</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.75803551454864e-05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0246386436720448</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0275626757079964</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rs633695</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0014690080413779</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.265377038355008</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0200369470092219</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>rs964184</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0068241736073854</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.57604390573947</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0198702813258398</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rs115478735</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0010085525625942</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.230655510794411</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0182364270638721</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>rs77542162</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0025068440034669</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.51932743824411</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0090675023779156</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>rs4299376</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0110004802960927</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.839874381087395</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.015260662988264</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rs102275</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0035346841701551</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.465564375064048</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0157827848629906</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rs4704834</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0004420774929385</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.181056373326278</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.01303591378256</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>rs72848251</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.001097920144743</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.312562684732685</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0109022730926698</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rs1883711</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0026183328066643</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.378757572331149</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.017603589742639</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>rs4665972</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0475495687819963</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.2436835728309</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0101520695397799</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>rs3777411</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0001221159239539</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.113387198495934</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.009213101241707501</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>rs11206517</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0004432765331851</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.186207865054844</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0123669195386764</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>rs2738447</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.40360177034389e-07</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.0039516272368703</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0087206358821771</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>rs34042070</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6.64536318825098e-05</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.0854642190823575</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0088273088062605</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rs926053</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0063880795996129</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.9183385785813311</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.007492872522917</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>rs77960347</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.52567522032412e-05</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.0475490506798757</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0065614634344714</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>rs56325564</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0102083101638427</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.16075536345842</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0075747466583702</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>rs472495</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0008374178035563</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.332311169061321</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0073847294072612</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>rs12804228</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0007682216627274</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.305904664831349</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.007986828315812501</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>rs72631343</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0024476516365675</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.590030464242026</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.006885484097573</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>rs553427</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.008556925042971</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.14567011477122</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0065198311846037</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>rs11854242</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0001807374039876</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.171304830285378</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.005995619462051</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>rs1169292</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0040875915404138</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.767426126206917</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.0068328467017961</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>rs838146</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.003506055442362</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.745998921267335</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0062018770555492</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>rs6601299</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.004465819049445</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.857366220872029</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.0060047893819372</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>rs10260606</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0015974765794443</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.479983923865586</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0067742114969711</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>rs2326077</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0252663524783417</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.18191136167903</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.005699229968082</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>rs2737245</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0068461028781992</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.1450852189421</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0052282642718615</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>rs653178</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0004708523426398</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.303401857672758</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0049911817630779</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>rs72843670</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0019434145997493</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-0.637507580568647</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0046992576005581</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>rs9616847</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0003002714266677</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.244832068552665</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0048851303361401</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>rs4939883</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0026339667490774</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.732403473439623</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0048383601113688</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>rs1500188</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0017239281247258</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.596469699484899</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0047563934992978</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>rs35633876</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0007571632680157</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.398961905540399</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.0046501032131393</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>rs6602911</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0010835092068676</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.48237847023895</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0045595643361751</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>rs72694391</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0020502786220657</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-0.69418518454949</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0041901019521363</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>rs12620918</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6.253624010151761e-05</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.11414530072464</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0046769499440162</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>rs72654473</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.107200804989635</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.646866527031165</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.202051673802752</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>rs12151108</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0001708923446292</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.0452859691297069</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.07549991833074569</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>rs157580</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0890371556525635</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.27810254446041</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.0523088353282824</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>rs11591147</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0444417411419786</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.847329508194793</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0579814684162396</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>rs12740374</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.008351088229694201</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.395176131088048</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0499478816895818</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>rs693</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.0014023762785545</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.169309084672756</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.0457756577362513</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>rs261290</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.0102896709008064</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.491936041201489</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.0401915236851357</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>rs112875651</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.288320352121567</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3.11318648727322</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.0337416768229954</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>rs58542926</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.820292790000002</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-5.70800440782147</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.0394581988825479</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>rs247616</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.002293606109291</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.294453188158714</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.0253130980005814</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>rs12916</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.007980788655125</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.5543806110443</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.0249683592626698</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>rs7534572</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.0032851089802103</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-0.379216970386467</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.0219598671323555</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>rs633695</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.0002927642360959</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-0.12120166349452</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.0191625869750526</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>rs964184</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.0050493387436295</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.515060726440303</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.0184085432643156</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>rs115478735</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.0088668992524136</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.713082780237581</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.0169733212346337</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>rs77542162</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.0055689955225544</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.619432062752882</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.0141325849744292</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>rs4299376</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1.08467133544917e-05</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.0263528734411676</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.0150756934116528</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>rs102275</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.0005995307919752</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.200068832724022</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.0144777065863634</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>rs4704834</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.0030936026565128</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-0.5016290611987601</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.0119652558686505</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>rs574454081</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.0013035111067629</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.25973523039377</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.0186088167651984</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>rs72848251</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.0025633479979434</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-0.462880108593703</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.0116387722720808</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>rs1883711</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.0222398481879793</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-1.32093212097247</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.0127705902204683</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>rs4665972</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.0812184621922125</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3.10768217558406</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.0097695104858817</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>rs3777411</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.0024158651157598</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-0.500693965466574</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.0094030191947024</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>rs11206517</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2.58298915169105e-05</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-0.0556429748445158</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.008109964341913901</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>rs2738447</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.0012713393102736</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.391134329228391</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.0081031896190013</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>rs34042070</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.0006419971795857</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.28155587551946</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.0078866640456583</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>rs926053</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.0005931758663472</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-0.27190045629649</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.0078133595345304</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>rs77960347</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.000208972045728</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-0.16217681374666</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.0077303560612875</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>rs56325564</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.0020894003471327</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-0.535573006365911</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.0071291543527246</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>rs472495</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.002898212338323</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-0.642626897237777</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.0068878179537796</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>rs12804228</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.0008190746604585</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-0.345304970963064</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.006703143016333</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>rs72631343</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.0001108672552806</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.130770685781958</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.006315512820778</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>rs553427</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0.0021338420221598</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.572897558580728</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.0063731917750832</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>rs11854242</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0.0001476583491637</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-0.151725416471197</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.0062495498045996</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>rs1169292</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0.0074044952121298</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-1.08815817999232</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.0062372070423153</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>rs838146</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0.00228825186092</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.610957895575427</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.0060170287738424</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>rs6601299</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0.0002075011653653</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.186526108477028</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.0058149081667006</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>rs10260606</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0.0004367115609</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.285822175376487</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.0052201068057757</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>rs2326077</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0.0089149421807197</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1.31905155921876</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.0051727588644506</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>rs2737245</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0.0024698882978753</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.70971767904588</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.0048313710319802</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>rs653178</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0.002434820833161</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.710716109517975</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.0047499276888984</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>rs72843670</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.0006612599676268</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-0.373495992410188</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.0046370580097996</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>rs532754706</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0.0003180502854486</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.223224076284904</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.0062225778623302</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>rs9616847</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.0011711280390674</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-0.498011670041425</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.0046294442719831</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>rs4939883</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.0013340550687923</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.541024269832261</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.0044730725329054</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>rs1500188</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>6.21534830513451e-07</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-0.0117051966558213</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.0044259743190184</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>rs35633876</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0.0005400825098373</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-0.346276392209324</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.0044053905532995</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>rs6602911</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0.0003370010489821</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.277851932228945</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.0042663588117024</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>rs72694391</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0.0005073207658</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-0.35338916734457</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.0039753720841184</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>rs12620918</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0.0020984476420167</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-0.716184159702219</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.0040349795116214</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>rs72654473</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0.102970932175263</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.722613487111973</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.163315168100054</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>rs12151108</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0.0126732038293626</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.396938561500437</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.07320933699913409</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>rs157580</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0.0542657915657326</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1.03081851470587</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.0486496948037521</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>rs11591147</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0.076012639429135</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-0.77403763259295</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.111733850064204</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>rs12740374</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0.0024341742324935</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.205722687388794</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.0533385648725237</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>rs693</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0.0132676920678082</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-0.501273969032726</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.0493937069143563</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>rs261290</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0.0007149676085158</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-0.119749605792638</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.046540982911216</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>rs112875651</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0.460097348905335</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3.88933975094909</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.0380525933817231</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>rs58542926</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0.385578789776321</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-4.53735350492209</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.025848176107153</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>rs247616</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>4.94387402959949e-05</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-0.0430083911098693</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.025493140577886</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>rs12916</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0.0032050578746759</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.326051621556006</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.0287255027051965</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>rs633695</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0.0015923234507773</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-0.265471935406426</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.0216673325886208</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>rs964184</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0.0175280245297171</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.890288040669849</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.0215423639188343</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>rs115478735</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1.11201617578158e-05</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-0.0235072476616834</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.0193153292954003</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>rs77542162</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0.0031605030326901</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-0.787531078210679</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.0050292986305356</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>rs4299376</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0.0125206539538921</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.977989084595512</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.0129096192079286</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>rs102275</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0.0001228008630609</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.0831925847500547</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.0170717990577548</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>rs4704834</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0.0178901464981854</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.18020632980148</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.0127857073336809</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>rs72848251</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0.00033141594863</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-0.201377648033622</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.0079420132330166</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>rs1883711</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0.0213263087536689</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-0.934130734910014</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.0237937632390941</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>rs4665972</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0.0098669174017445</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.969271692012768</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.0103800480417943</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>rs3777411</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0.0005046360247698</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.234283996879387</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.0089284463720246</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>rs11206517</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0.0002967318740108</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-0.152628373170662</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.0123194131748306</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>rs2738447</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0.0054865220358286</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-0.780244463107358</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.0088581178882704</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>rs34042070</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>9.54312939360277e-05</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-0.100758136507916</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.009118181455451501</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>rs926053</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0.0092557141349502</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-1.25223142157534</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.0059384324217838</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>rs77960347</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0.0004538968336568</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.314413301003341</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.0044832832411521</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>rs56325564</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0.0001677443094652</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-0.144465866254158</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.007808538564671</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>rs472495</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0.0035856349230379</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.653209453465037</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.0082326705901611</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>rs12804228</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0.0006982228186397001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.230517646736416</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.0127113362451685</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>rs72631343</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0.009077732936087501</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-1.08617125997315</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.0076647352034432</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>rs553427</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>0.0003127997791914</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.209231474623587</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.0069511412596433</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>rs11854242</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0.0006089459504879</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.328178259753521</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.0055161046362533</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>rs1169292</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0.0006789068301626</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.303314058051295</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.0071849071372526</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>rs838146</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0.0016419227726035</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.498727916934335</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.0064537982463203</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>rs6601299</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0.0211618385328613</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.64047756937122</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.0080805612599148</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>rs10260606</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0.0081297040451354</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.970644998872693</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.008544609241674</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>rs2326077</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0.0033349956266194</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.743435908859128</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.0059411060386322</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>rs2737245</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>6.80136042111197e-05</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-0.107952306891198</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.0056810373087989</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>rs653178</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0.0014201998526353</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.521432312499693</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.005116174506577</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>rs72843670</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0.0029935235509688</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-0.783850024116754</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.0048088988920638</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>rs9616847</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2.05353115590581e-05</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.0620566258729425</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.0051923079768744</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>rs4939883</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0.0004152658845924</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.292289305302479</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.0047435253959684</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>rs1500188</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>0.0032285845805379</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.804146437562926</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.0049308044723465</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>rs35633876</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0.0077201716303221</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-1.27548973616843</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.0047856821919574</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>rs6602911</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>4.94952361232661e-05</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.101607998347206</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.0046712337471397</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>rs72694391</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0.0016641270471598</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-0.62809186598524</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.0041467145104727</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>rs12620918</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0.0057494944642041</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1.13765232578483</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.0044502460372936</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G148"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SNP</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Wj</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>BetaWj</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Qj</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Qj_Chi</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Outliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>rs72654473</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10.3389867466554</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.07228427469966</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.377983082181583</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.53868463803543</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rs12151108</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5.62260233460678</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.168630980798834</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.174240045453939</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.676370712516718</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rs157580</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4.91031387968822</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.06686960778819</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.21730417166109</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0223631934093964</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rs11591147</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5.07910725152703</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.469569370271598</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.482066994983054</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.487487541638047</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rs12740374</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4.95708846386461</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.992120904135089</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.597187280470304</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.439653222830815</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rs693</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4.75191020455665</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.34135115582797</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.27935993452315</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.25801807855396</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rs261290</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4.41217068173769</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.421247697704222</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.380045206970494</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.53757904333939</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rs112875651</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4.12459388203632</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.92131709006222</v>
+      </c>
+      <c r="E9" t="n">
+        <v>32.9339569834015</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.53432891801562e-09</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rs58542926</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3.68232489851831</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-8.348240038813421</v>
+      </c>
+      <c r="E10" t="n">
+        <v>72.4401183632211</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.72177928425736e-17</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rs247616</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3.48433303680503</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.801435169446213</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.418945371845304</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5174637528068931</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rs12916</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3.55883399929732</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.106216204604875</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0026271364411282</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.95912184833777</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rs633695</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3.03433794763777</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.419575689775501</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.306738209508392</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.579688681829085</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>rs964184</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3.02168314900649</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.33262201965273</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.43740471786683</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.230559775609412</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rs115478735</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2.89478632293609</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.610005335371211</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.232243425922416</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.629865328467112</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>rs77542162</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2.04128533547361</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.997244719240073</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.18280373974423</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.276785948177009</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>rs4299376</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2.64810880212724</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.6279344497683</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.04540316261078</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.08096600990951359</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rs102275</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2.69301793759828</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.853034780171132</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.945164729997315</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.330953135187211</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rs4704834</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.44747561807264</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.487669388504795</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.143923973176006</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.704410799633837</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>rs72848251</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2.23824658870729</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.754205531581981</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.429244153536763</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.512360063802859</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rs1883711</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2.84402378190132</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.916645318153566</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.625368658464646</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.429059227055139</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>rs4665972</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2.15985691001705</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.56700136704756</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19.9937014904404</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7.76976733608023e-06</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>rs3777411</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2.05756069171016</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.147046387154761</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0566866726297313</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.811811576401637</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>rs11206517</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2.38378557392498</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.284794371324137</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.152312594319315</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.696335084407574</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>rs2738447</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2.00180407043022</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0968806439022302</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6.89651625490466e-05</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.993374022577471</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>rs34042070</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2.01400627429245</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.268624144862253</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0322231589353795</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.857538755631675</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rs926053</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.85555758952197</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.83073297489411</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.65894904834986</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0557688003119949</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>rs77960347</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.73641152547868</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.176826471543414</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0099986964722301</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.920349500002953</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>rs56325564</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.86565628140412</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.48731838166878</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.78290216741042</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.016182799771428</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>rs472495</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1.84210924950051</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.616183820563576</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.486776552328312</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.485368745009246</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>rs12804228</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1.91571409314144</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.557401367498447</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.412379949507757</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.520764002102191</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>rs72631343</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.7787500956073</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.15720551006073</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.5274782311272</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.216491312176666</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>rs553427</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1.73088081023191</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-2.29906121077645</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.64371043414727</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.0175180954251807</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>rs11854242</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1.65984391727152</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.286781722723859</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.129763302387612</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.718677581396811</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>rs1169292</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1.77193325554361</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.68178563466677</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.57083022903504</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.108850590879794</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>rs838146</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1.68814661058338</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.63435571105494</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.4325341831518</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.118840638493325</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>rs6601299</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1.66110413949436</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-1.71573370881326</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.2013600460865</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.073577059928383</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>rs10260606</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1.7642977476629</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.928658538162041</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.01349611389173</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.314066732750092</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>rs2326077</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1.61828276376271</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4.44140665480331</v>
+      </c>
+      <c r="E39" t="n">
+        <v>19.095157668437</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.24360016551807e-05</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>rs2737245</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1.54998060170506</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.44459476655016</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5.64542827093242</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0175009410890535</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>rs653178</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1.51443236554531</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.5708823944377101</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.406907757214433</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.523543193013168</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>rs72843670</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1.46948023587754</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.40102182578952</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.7848961359223</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.181549256677684</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>rs9616847</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1.4982552585093</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.581258241040263</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.265187122833441</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.606578718462132</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>rs4939883</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1.49106367917148</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-1.46662758551824</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.34887620941958</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.125373359736711</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>rs1500188</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1.47838117477091</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-1.18521986135071</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.56408911961318</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.21106749754091</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>rs35633876</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1.46177061316356</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.773658735893067</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.702812906514775</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.401840128066649</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>rs6602911</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1.44747051500883</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.0769165537818</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.02590293899557</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.311122895816199</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>rs72694391</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1.3875873132017</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.51536136848186</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.11400899712919</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.145956508156647</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>rs12620918</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1.46597205250321</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.175360653722459</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.057709106675913</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.810154129940996</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>rs72654473</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>7.83169725872663</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.29615157396123</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.69838089464262</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.192499856966667</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>rs12151108</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4.78738004976754</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.0943006709299698</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.009726127469371799</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.9214390917403</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>rs157580</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3.98485194279562</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-2.77589433104256</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7.6856369072765</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.0055662032278028</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>rs11591147</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4.19536034235632</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-1.85299246175729</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3.41956386938378</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.06442803214251699</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>rs12740374</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3.89388572250841</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.87454873038579</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.758701310831108</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.383735249894079</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>rs693</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3.72770864840874</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.377854345436109</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.140242914053317</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.708039642206709</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>rs261290</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3.49294622880534</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-1.09206500442238</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.18573093408193</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.276192371881607</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>rs112875651</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3.20042751398482</v>
+      </c>
+      <c r="D57" t="n">
+        <v>6.33030222492659</v>
+      </c>
+      <c r="E57" t="n">
+        <v>40.109302038004</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.40142741355614e-10</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>rs58542926</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>3.46093379043426</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-9.823023520123719</v>
+      </c>
+      <c r="E58" t="n">
+        <v>96.4304386841989</v>
+      </c>
+      <c r="F58" t="n">
+        <v>9.2435069272861e-23</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>rs247616</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2.77202609855276</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.660351676529001</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.432766635795966</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.510634515511075</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>rs12916</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2.75308529648422</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-1.23849347493378</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.52771800579584</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.216455254719842</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>rs7534572</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2.58190060155224</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.845857081658675</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.719421468222837</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.396333743637172</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>rs633695</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2.41185799603214</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.269657480523617</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.07389378148672179</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.7857495790956081</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>rs964184</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2.36392871289757</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.15055867496198</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.32869895365436</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.249036807201062</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>rs115478735</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2.26990708131992</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.59105046437465</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.53796437335591</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.111137987206695</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>rs77542162</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2.07126405215282</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-1.38949110454078</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.92549440924842</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.165252223240545</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>rs4299376</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2.13925873014472</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.0573057315465265</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.0035089446055808</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.952763861086023</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>rs102275</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2.09640192598704</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.447781566117161</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.202206259265286</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.652945879838425</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>rs4704834</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1.90583658605884</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.12474703973235</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.26892789611163</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.259967902232525</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>rs574454081</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2.37675294229099</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.584536573274792</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.339180008889433</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.560302919128734</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>rs72848251</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1.87965545520698</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.03832173688375</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.08163757937562</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.29833150699027</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>rs1883711</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1.96892941839467</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2.91937064366653</v>
+      </c>
+      <c r="E71" t="n">
+        <v>8.533102953831181</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.0034874462925198</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>rs4665972</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1.72211070366798</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6.40024815975082</v>
+      </c>
+      <c r="E72" t="n">
+        <v>40.9830728231245</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.53553408173133e-10</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>rs3777411</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1.68950050471991</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-1.1273595146751</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.26750398242208</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.260235453847133</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>rs11206517</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1.56904043963196</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.124097457174325</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.0157536303614285</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.9001170643398611</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>rs2738447</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1.56838494727405</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-0.88235113222511</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.776047732390631</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.378352615789614</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>rs34042070</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1.54728863381238</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-0.636078353180459</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.4028212078958</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.525635852646141</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>rs926053</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1.54008102135116</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-0.614362661040989</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.375735636777707</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.539894333967103</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>rs77960347</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1.53187882600521</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.364422021517726</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.133812927836484</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.71451096623315</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>rs56325564</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1.47110500609216</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1.20387360238305</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.45251000096373</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.228125628287842</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>rs472495</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1.44599068337465</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1.4431285806621</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.08638825668655</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.148617061345297</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>rs12804228</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1.426474153742</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.777244795432541</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.606112298492654</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.436255364746458</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>rs72631343</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1.38461481868558</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.293953472123879</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.087144836877735</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.767838777187115</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>rs553427</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1.39092322271102</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-1.29039775970727</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.6618883729779</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.197348552308931</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>rs11854242</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1.37736496267716</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-0.343740179769058</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.117304298568948</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.731976787535435</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>rs1169292</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1.37600415326769</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2.42654399230565</v>
+      </c>
+      <c r="E85" t="n">
+        <v>5.8941438557375</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.015191312690206</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>rs838146</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1.35149893788656</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1.37318553852971</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.88898971932067</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.169315915312916</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>rs6601299</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1.3286056489314</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-0.422294983306162</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.177321806238799</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.673685012654588</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>rs10260606</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1.25882210112514</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-0.646284463282931</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.416216478543532</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.5188310109666751</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>rs2326077</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1.25310014798087</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2.92720441620321</v>
+      </c>
+      <c r="E89" t="n">
+        <v>8.57514762746448</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.0034078232557751</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>rs2737245</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1.2110438265563</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1.59432740550743</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2.54536604372097</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.11061827178493</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>rs653178</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1.20079304462962</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-1.59879094000438</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2.55266849512752</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.110108141828609</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>rs72843670</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1.18644040672059</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.841723019859439</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.7103012966687841</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.399343806851992</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>rs532754706</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1.3743895103299</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.502523312939647</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.253777821381329</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.614427469907019</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>rs9616847</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1.18546597860928</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1.12145906156215</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.26007114782781</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.261637623706086</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>rs4939883</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1.16527286865052</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-1.22007463918205</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.48601711608562</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.2228354565139</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>rs1500188</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1.15912189501005</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-0.0274991882497375</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.0006997674081743</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.978895927574844</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>rs35633876</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1.15642340454336</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-0.782663109748186</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.610929002095997</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.434438238722412</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>rs6602911</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1.13802906412668</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-0.628514571994647</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.393740608506638</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.530339703453847</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>rs72694391</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1.0985341350713</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.796814959300057</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.6364949750166849</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.424982874707241</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>rs12620918</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1.10673929840274</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1.60945204381309</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2.59355191205956</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.10729946907067</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>rs72654473</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2.88568106459758</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.521844738906261</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.996835114577326</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.318077531252739</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>rs12151108</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1.93201979443494</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.26040728470622</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.335798517456955</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.562264495562334</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>rs157580</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1.57495911151915</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-1.77009515459352</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2.28006958228881</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.131045994259819</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>rs11591147</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2.38655790405963</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-1.49506592949909</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1.21203538508623</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.270929393408893</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>rs12740374</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1.6490893612784</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.576273046115384</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.0923705115835988</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.761184898107488</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>rs693</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1.58693585312294</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.478303837956141</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.548172952853606</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.459065187001179</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>rs261290</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1.54041660759997</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-0.432003393550792</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.0315427820446509</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.859034864669511</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>rs112875651</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1.39288055181645</v>
+      </c>
+      <c r="D108" t="n">
+        <v>4.7966720616313</v>
+      </c>
+      <c r="E108" t="n">
+        <v>25.2677825589317</v>
+      </c>
+      <c r="F108" t="n">
+        <v>4.98974015848385e-07</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>rs58542926</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1.14801282071004</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-5.84389834935474</v>
+      </c>
+      <c r="E109" t="n">
+        <v>31.9711480735849</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.56479499708565e-08</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>rs247616</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1.14008621902681</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-0.2527857536989</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.0041602482701706</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.94857211779027</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>rs12916</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1.21019320484273</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-0.687428686310427</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.237719354261944</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.625858191492778</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>rs633695</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1.05105105359659</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.224976762423186</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.158848742989319</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.690218670130064</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>rs964184</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1.04801027636639</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1.15326730176481</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1.7591955269469</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.184724890049724</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>rs115478735</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0.9923629638710511</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-0.128533830261066</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.0012500023886334</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.971796369759683</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>rs77542162</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0.506415138948635</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1.10176552391451</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1.40517367840006</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.235859245326495</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>rs4299376</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0.811313702068754</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1.32691895440277</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2.13425156522336</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.144040749038418</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>rs102275</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0.932952370978085</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-0.0288035257423278</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.01569357267722</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.900306642584085</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>rs4704834</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0.807396421022997</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-1.88827355571894</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3.07978514123008</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.07927099747828539</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>rs72848251</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0.636359323862054</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.199461822391795</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.0927548806443502</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.760703681058682</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>rs1883711</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1.10130832309437</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1.20686039406015</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1.92860426950277</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.164911225736757</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>rs4665972</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0.727482323450942</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.32982729154082</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2.10241686998871</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.147066513164145</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>rs3777411</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0.67470825835477</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.242656667425363</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.125376221774402</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.723275146528604</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>rs11206517</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0.792504129495199</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.09946283059144841</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.053058936330328</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.817823497787459</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>rs2738447</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0.672037433473946</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.06124411007451</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.37412646328112</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.241104163564838</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>rs34042070</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0.681827938284346</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.0397309580976973</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.0232060003315311</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.878922596508303</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>rs926053</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0.55026455519143</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-1.95595568023826</v>
+      </c>
+      <c r="E126" t="n">
+        <v>3.47852054943692</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.0621702988372187</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>rs77960347</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0.478123455273021</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.555011965058064</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.22662327400149</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.634039002830431</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>rs56325564</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0.630967679134204</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.114333606848775</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.0477589497953008</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.827009789411022</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>rs472495</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0.647873064872928</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-1.09060515547325</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.967485914867687</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.325307985799128</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>rs12804228</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0.804978135915516</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.480653861651601</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.120903182693397</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.728056972133025</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>rs72631343</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0.625125946478874</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-1.72615963503344</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2.63386866243916</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.104606551290595</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>rs553427</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>0.59532088216904</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-0.414896789711255</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.100222434380797</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.751562867228601</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>rs11854242</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0.530330907618725</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.408981826432314</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.246578012285861</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.619494978188919</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>rs1169292</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0.6052436164466261</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-0.558588551323618</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.210343575363226</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.646498246379513</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>rs838146</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0.573629041938043</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.65837177665219</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.5671699706054421</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.451385691265692</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>rs6601299</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0.641845449447052</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-2.51824530405063</v>
+      </c>
+      <c r="E136" t="n">
+        <v>5.81892222903171</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.0158546571004458</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>rs10260606</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0.6600071990113801</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-1.5622720134718</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2.11199810755788</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.146148381803664</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>rs2326077</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5503682389408689</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.0283458103618</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.25269678958264</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.263038029494727</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>rs2737245</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0.538187435493511</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-0.252381623165467</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.0267321580901033</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.870124994434784</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>rs653178</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0.510735591267542</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-0.872079615010516</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.6205207515558731</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.430853837263744</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>rs72843670</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0.495162582096599</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1.09821105933407</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1.39237023844481</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.238005230631898</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>rs9616847</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0.51451892333664</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-0.178993875330042</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.0088399177599436</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.925092604650278</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>rs4939883</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0.491783844990852</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-0.52375850835226</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.19584180965769</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.6580983625106011</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>rs1500188</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>0.5013959352165011</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1.12723436993131</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1.46419714248314</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.226263490400277</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>rs35633876</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0.493963424889256</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-1.9811699424119</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3.6084484519845</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.0574867283338645</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>rs6602911</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0.488021609862332</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-0.234569387100376</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.0237074975604583</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.877631503803509</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>rs72694391</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0.459808221964243</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.872128057116121</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.898828377989365</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.343096060416275</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>rs12620918</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0.476335369420063</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-1.77920321533683</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2.89182339628417</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.08903011165563129</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>spearman</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sign_concordance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ghodsian 2021</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fairfield 2022</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6784628745115067</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.163885712450409e-07</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ghodsian 2021</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FinnGen R5</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4866478506296135</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0004527059929442</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fairfield 2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FinnGen R5</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3275075987841945</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0230685535304723</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/results/Supplementary_Tables.xlsx
+++ b/results/Supplementary_Tables.xlsx
@@ -33,6 +33,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S10 Influence diagnostics" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S11 Radial MR" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S12 Cross-dataset concordance" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S13 Dataset characteristics" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S14 Diagnostics summary" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S15 Sensitivity analyses" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S16 Positive control summary" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30668,6 +30672,642 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Design / source</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variants used</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2 (%)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Mean F (min)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MDE, OR*</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Exposure: RC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UK Biobank NMR GWAS (Richardson 2022); N = 115,082</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>150 (29.8)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ghodsian 2021</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EHR meta-analysis of 4 cohorts; GCST90091033</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8,434</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>770,180</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>150 (29.8)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fairfield 2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UK Biobank; GCST90054782</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4,761</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>373,227</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>147 (29.8)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FinnGen R5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FinnGen; finn-b-NAFLD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>217,898</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>150 (29.8)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Positive control: CAD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CARDIoGRAMplusC4D 1000G (Nikpay 2015); GCST003116</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>60,801</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>123,504</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>150 (29.8)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SNPs</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QIVW (P)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>I2 (%)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>I2GX (%)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Egger intercept (P)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MR-PRESSO outliers</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Radial outliers</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Cook &gt; 4/n</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ghodsian</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>204.8 (1.4 × 10−21)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>99.3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.0112 (.261)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>rs112875651, rs58542926, rs4665972, rs2326077</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>251.4 (1.2 × 10−28)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>80.1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>99.3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.0211 (.118)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>rs112875651, rs58542926, rs4665972</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>106.2 (1.8 × 10−6)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>99.3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>−0.0013 (.952)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>rs112875651, rs58542926</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ghodsian: OR (95% CI), P</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Fairfield: OR (95% CI), P</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FinnGen: OR (95% CI), P</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>All variants</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.045 (0.864–1.265), .650 [48]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.999 (0.776–1.286), .994 [51]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.848 (0.561–1.281), .433 [48]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MR-PRESSO outliers removed</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.023 (0.914–1.145), .695 [44]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.009 (0.871–1.169), .908 [48]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.839 (0.624–1.127), .250 [46]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Steiger-filtered</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.081 (0.943–1.238), .263 [45]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.996 (0.865–1.146), .951 [47]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.949 (0.706–1.275), .727 [35]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>APOE region excluded</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.073 (0.853–1.349), .548 [45]</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.014 (0.748–1.374), .930 [47]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.859 (0.539–1.369), .523 [45]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F ≥ 30 only</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.046 (0.862–1.269), .648 [47]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.993 (0.770–1.280), .958 [50]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.861 (0.570–1.301), .478 [47]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Earlier 48-variant set</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.984 (0.869–1.114), .798 [41]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.990 (0.851–1.152), .898 [48]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.752 (0.562–1.006), .055 [43]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -34267,6 +34907,209 @@
       </c>
       <c r="T52" t="n">
         <v>0.0001630063367049</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SNPs</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IVW</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.378–1.809</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5.2 × 10−11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MR-Egger</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.871</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.461–2.395</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9.4 × 10−6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Weighted median</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.475</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.321–1.648</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5.6 × 10−12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Simple mode</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.408</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.088–1.821</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>.012</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Weighted mode</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.393</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.216–1.597</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.7 × 10−5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IVW after MR-PRESSO outlier removal (R)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.492</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.348–1.651</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.4 × 10−9</t>
+        </is>
       </c>
     </row>
   </sheetData>
